--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486879_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486879_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.188</v>
+        <v>5.8048</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4072</v>
+        <v>5.7869</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2192</v>
+        <v>0.018</v>
       </c>
       <c r="G2" t="n">
         <v>5.1659</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5765</v>
+        <v>1.1933</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2517</v>
+        <v>0.6314</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3248</v>
+        <v>0.5619</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3491</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.259</v>
+        <v>1.6499</v>
       </c>
       <c r="E3" t="n">
-        <v>2.588</v>
+        <v>1.3655</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.329</v>
+        <v>0.2845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4731</v>
+        <v>3.9406</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4282</v>
+        <v>-0.7106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0448</v>
+        <v>4.6512</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0617</v>
+        <v>3.4105</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7855</v>
+        <v>-1.1932</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2763</v>
+        <v>4.6037</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5887</v>
+        <v>0.5301</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3572</v>
+        <v>0.4826</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2314</v>
+        <v>0.0475</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4841</v>
+        <v>-0.2373</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0725</v>
+        <v>-0.1435</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4116</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
         <v>-1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.37</v>
+        <v>1.4847</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2337</v>
+        <v>0.1523</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1362</v>
+        <v>1.3324</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9406</v>
+        <v>0.7369</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7106</v>
+        <v>0.7975</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6512</v>
+        <v>-0.0605</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4105</v>
+        <v>1.1831</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1932</v>
+        <v>1.0122</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6037</v>
+        <v>0.1709</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5301</v>
+        <v>-0.4462</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4826</v>
+        <v>-0.2147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0475</v>
+        <v>-0.2314</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5172</v>
+        <v>0.7478</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2753</v>
+        <v>-0.0041</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2419</v>
+        <v>0.7518</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.109</v>
+        <v>1.4428</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8162</v>
+        <v>1.7125</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9252</v>
+        <v>-0.2697</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7369</v>
+        <v>0.4731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7975</v>
+        <v>0.4282</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0605</v>
+        <v>0.0448</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1831</v>
+        <v>1.0617</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0122</v>
+        <v>0.7855</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1709</v>
+        <v>0.2763</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4462</v>
+        <v>-0.5887</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2147</v>
+        <v>-0.3572</v>
       </c>
       <c r="O5" t="n">
         <v>-0.2314</v>
@@ -844,22 +844,22 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3721</v>
+        <v>1.6678</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9726</v>
+        <v>1.197</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3447</v>
+        <v>0.4709</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9273</v>
+        <v>1.2016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2214</v>
+        <v>0.7328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.706</v>
+        <v>0.4688</v>
       </c>
       <c r="G6" t="n">
         <v>1.2098</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8205</v>
+        <v>-0.5462</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1702</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3498</v>
+        <v>0.1126</v>
       </c>
       <c r="V6" t="n">
         <v>-0.4887</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.769</v>
+        <v>0.7623</v>
       </c>
       <c r="E7" t="n">
-        <v>1.708</v>
+        <v>1.5531</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>2.2097</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4668</v>
+        <v>0.4601</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2903</v>
+        <v>0.1354</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1765</v>
+        <v>0.3247</v>
       </c>
       <c r="V7" t="n">
         <v>-1.9076</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9731</v>
+        <v>-1.2154</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7141</v>
+        <v>-2.1639</v>
       </c>
       <c r="F8" t="n">
-        <v>0.741</v>
+        <v>0.9485</v>
       </c>
       <c r="G8" t="n">
         <v>-0.06950000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4231</v>
+        <v>-0.6654</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1198</v>
+        <v>-0.5697</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3033</v>
+        <v>-0.0958</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4805</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0352</v>
+        <v>-2.3236</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3608</v>
+        <v>-0.1351</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.396</v>
+        <v>-2.1885</v>
       </c>
       <c r="G9" t="n">
         <v>1.4303</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0642</v>
+        <v>0.7758</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2512</v>
+        <v>0.7553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.187</v>
+        <v>0.0205</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4497</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8264</v>
+        <v>-2.4171</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1733</v>
+        <v>-3.7936</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3469</v>
+        <v>1.3765</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2385</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1197</v>
+        <v>0.2896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.283</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1633</v>
+        <v>0.1929</v>
       </c>
       <c r="V10" t="n">
         <v>0.5585</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0697</v>
+        <v>-7.3547</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.322100000000001</v>
+        <v>-8.3995</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2524</v>
+        <v>1.0449</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8317</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6676</v>
+        <v>0.3826</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2826</v>
+        <v>0.2051</v>
       </c>
       <c r="U11" t="n">
-        <v>0.385</v>
+        <v>0.1775</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0308</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.282100000000002</v>
+        <v>-0.9646999999999979</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.506600000000001</v>
+        <v>-3.189</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2245</v>
+        <v>2.2246</v>
       </c>
       <c r="G12" t="n">
-        <v>8.0266</v>
+        <v>8.026600000000002</v>
       </c>
       <c r="H12" t="n">
         <v>4.2141</v>
@@ -1369,7 +1369,7 @@
         <v>1.495299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>7.981499999999999</v>
+        <v>7.9815</v>
       </c>
       <c r="M12" t="n">
         <v>-1.45</v>
@@ -1390,13 +1390,13 @@
         <v>10.2671</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7508</v>
+        <v>4.0681</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3274000000000001</v>
+        <v>1.6448</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4235</v>
+        <v>2.4233</v>
       </c>
       <c r="V12" t="n">
         <v>-4.846100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4055</v>
+        <v>10.6757</v>
       </c>
       <c r="E13" t="n">
         <v>9.099500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.306</v>
+        <v>1.5762</v>
       </c>
       <c r="G13" t="n">
         <v>4.3995</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2692</v>
+        <v>0.001</v>
       </c>
       <c r="T13" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4168</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.0164</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3621</v>
+        <v>3.0038</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6278</v>
+        <v>-0.209</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7343</v>
+        <v>3.2129</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0232</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1245</v>
+        <v>0.7663</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9064</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2181</v>
+        <v>0.6967</v>
       </c>
       <c r="V14" t="n">
         <v>3.0554</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0913</v>
+        <v>2.48</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8628</v>
+        <v>1.2812</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2284</v>
+        <v>1.1988</v>
       </c>
       <c r="G15" t="n">
         <v>0.5643</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6435</v>
+        <v>-0.2547</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7246</v>
+        <v>-0.3062</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0514</v>
       </c>
       <c r="V15" t="n">
         <v>0.9384</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.373</v>
+        <v>0.9797</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9254</v>
+        <v>1.6185</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5524</v>
+        <v>-0.6388</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6083</v>
+        <v>-0.1536</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7421</v>
+        <v>0.0488</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1338</v>
+        <v>-0.2023</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6313</v>
+        <v>1.7264</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2103</v>
+        <v>0.5164</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.579</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.023</v>
+        <v>-1.88</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5318000000000001</v>
+        <v>-0.4676</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5548</v>
+        <v>-1.4124</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9546</v>
+        <v>-0.5792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9222</v>
+        <v>-0.5349</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0324</v>
+        <v>-0.0443</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4189</v>
+        <v>1.6591</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6417</v>
+        <v>0.6644</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5725</v>
+        <v>-0.6116</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2142</v>
+        <v>1.276</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1536</v>
+        <v>0.6083</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0488</v>
+        <v>1.7421</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2023</v>
+        <v>-1.1338</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7264</v>
+        <v>0.6313</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5164</v>
+        <v>1.2103</v>
       </c>
       <c r="L17" t="n">
-        <v>1.21</v>
+        <v>-0.579</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.88</v>
+        <v>-0.023</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4676</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4124</v>
+        <v>-0.5548</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2006</v>
+        <v>-0.9172</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5809</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6197</v>
+        <v>-0.3088</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6591</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5678</v>
+        <v>-1.7003</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1934</v>
+        <v>-0.821</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3744</v>
+        <v>-0.8792</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1677</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.3873</v>
       </c>
       <c r="T18" t="n">
-        <v>0.945</v>
+        <v>0.3174</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4252</v>
+        <v>0.0699</v>
       </c>
       <c r="V18" t="n">
         <v>-1.7679</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5788</v>
+        <v>-1.8596</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6977</v>
+        <v>-3.0115</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1189</v>
+        <v>1.152</v>
       </c>
       <c r="G19" t="n">
         <v>-4.22</v>
@@ -1936,13 +1936,13 @@
         <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6226</v>
+        <v>0.3419</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1159</v>
+        <v>-0.1979</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5067</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2402</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4275</v>
+        <v>-2.8233</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5138</v>
+        <v>-4.4553</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0863</v>
+        <v>1.632</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8683999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2088</v>
+        <v>-0.1869</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7746</v>
+        <v>-0.1668</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5659</v>
+        <v>-0.0201</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7679</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.9878</v>
+        <v>-7.0464</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0567</v>
+        <v>-5.1153</v>
       </c>
       <c r="F21" t="n">
         <v>-1.9311</v>
@@ -2092,10 +2092,10 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1585</v>
+        <v>-0.217</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2516</v>
+        <v>-0.3101</v>
       </c>
       <c r="U21" t="n">
         <v>0.0931</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.282299999999999</v>
+        <v>4.374000000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.224399999999998</v>
+        <v>-2.224499999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>4.506600000000001</v>
+        <v>6.5988</v>
       </c>
       <c r="G22" t="n">
         <v>-8.026900000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.214</v>
+        <v>-4.214000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>-3.8126</v>
@@ -2146,13 +2146,13 @@
         <v>1.4499</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.718899999999999</v>
+        <v>-2.7189</v>
       </c>
       <c r="L22" t="n">
         <v>4.168800000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.476600000000001</v>
+        <v>-9.476599999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-1.495</v>
@@ -2170,13 +2170,13 @@
         <v>18.4808</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7508</v>
+        <v>-0.6585000000000002</v>
       </c>
       <c r="T22" t="n">
         <v>-2.4234</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3274000000000001</v>
+        <v>1.7647</v>
       </c>
       <c r="V22" t="n">
         <v>4.8461</v>
